--- a/Среда.xlsx
+++ b/Среда.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Desktop\Посещаемость\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Documents\Folder\Generator_rep_attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -87,7 +87,7 @@
     <t>Кинетов Жан Бахытович</t>
   </si>
   <si>
-    <t>Абдрахман Хасен Алпамысович</t>
+    <t>Абдрахманов Хасен Алпамысович</t>
   </si>
 </sst>
 </file>
